--- a/public/exports-60-250-with-coowners/29189765.xlsx
+++ b/public/exports-60-250-with-coowners/29189765.xlsx
@@ -2614,7 +2614,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928758</t>
+          <t xml:space="preserve">311928752</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
